--- a/samples/ar_trial_balance_customers_sample.xlsx
+++ b/samples/ar_trial_balance_customers_sample.xlsx
@@ -413,13 +413,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S7"/>
+  <dimension ref="A1:R7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Customer Number</t>
+          <t>Collector ID</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
@@ -429,77 +429,77 @@
       </c>
       <c r="C1" t="inlineStr">
         <is>
+          <t>Customer</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
           <t>Customer Segment</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>Country</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>Account Owner</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>Payment Terms</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>Credit Limit</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>Region</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Currency</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>Last Payment Date</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>DSO</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>Risk Rating</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>Sales Rep</t>
         </is>
       </c>
-      <c r="N1" t="inlineStr">
+      <c r="O1" t="inlineStr">
         <is>
           <t>Branch</t>
         </is>
       </c>
-      <c r="O1" t="inlineStr">
+      <c r="P1" t="inlineStr">
         <is>
           <t>Opening Balance</t>
         </is>
       </c>
-      <c r="P1" t="inlineStr">
-        <is>
-          <t>Closing Balance</t>
-        </is>
-      </c>
       <c r="Q1" t="inlineStr">
         <is>
-          <t>Account stop/Open</t>
+          <t>Account Stop/Open</t>
         </is>
       </c>
       <c r="R1" t="inlineStr">
@@ -511,72 +511,74 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>ACME LOGISTICS</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
           <t>1004000001</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>ACME LOGISTICS</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t>Enterprise</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t>Cameroon</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>Aurelie Uguebou</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>15 days</t>
         </is>
       </c>
-      <c r="G2" t="n">
+      <c r="H2" t="n">
         <v>9000000</v>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>Littoral</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="J2" t="inlineStr">
         <is>
           <t>XAF</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
-      <c r="K2" t="n">
+      <c r="L2" t="n">
         <v>45</v>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>Rep 1</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t>Douala</t>
         </is>
-      </c>
-      <c r="O2" t="n">
-        <v>4500000</v>
       </c>
       <c r="P2" t="n">
         <v>4500000</v>
@@ -595,72 +597,74 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>BETA TRADING SARL</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
           <t>1004000002</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>BETA TRADING SARL</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>Field Sales</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>Cameroon</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>Aurelie Uguebou</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>15 days</t>
         </is>
       </c>
-      <c r="G3" t="n">
+      <c r="H3" t="n">
         <v>1340000</v>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t>Littoral</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="J3" t="inlineStr">
         <is>
           <t>XAF</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
-      <c r="K3" t="n">
+      <c r="L3" t="n">
         <v>45</v>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t>Rep 1</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="O3" t="inlineStr">
         <is>
           <t>Douala</t>
         </is>
-      </c>
-      <c r="O3" t="n">
-        <v>670000</v>
       </c>
       <c r="P3" t="n">
         <v>670000</v>
@@ -671,72 +675,74 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>GAMMA SARL</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
           <t>1004000003</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>GAMMA SARL</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
+      <c r="D4" t="inlineStr">
         <is>
           <t>Telesales</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="E4" t="inlineStr">
         <is>
           <t>Cameroon</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="F4" t="inlineStr">
         <is>
           <t>Aurelie Uguebou</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>15 days</t>
         </is>
       </c>
-      <c r="G4" t="n">
+      <c r="H4" t="n">
         <v>1000000</v>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="I4" t="inlineStr">
         <is>
           <t>Littoral</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="J4" t="inlineStr">
         <is>
           <t>XAF</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
-      <c r="K4" t="n">
+      <c r="L4" t="n">
         <v>45</v>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="M4" t="inlineStr">
+      <c r="N4" t="inlineStr">
         <is>
           <t>Rep 1</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="O4" t="inlineStr">
         <is>
           <t>Douala</t>
         </is>
-      </c>
-      <c r="O4" t="n">
-        <v>500000</v>
       </c>
       <c r="P4" t="n">
         <v>500000</v>
@@ -755,72 +761,74 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>DELTA CORP</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
           <t>1004000004</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>DELTA CORP</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
+      <c r="D5" t="inlineStr">
         <is>
           <t>New Customer</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="E5" t="inlineStr">
         <is>
           <t>Cameroon</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="F5" t="inlineStr">
         <is>
           <t>Aurelie Uguebou</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t>15 days</t>
         </is>
       </c>
-      <c r="G5" t="n">
+      <c r="H5" t="n">
         <v>4800000</v>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="I5" t="inlineStr">
         <is>
           <t>Littoral</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="J5" t="inlineStr">
         <is>
           <t>XAF</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
-      <c r="K5" t="n">
+      <c r="L5" t="n">
         <v>45</v>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="N5" t="inlineStr">
         <is>
           <t>Rep 1</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
+      <c r="O5" t="inlineStr">
         <is>
           <t>Douala</t>
         </is>
-      </c>
-      <c r="O5" t="n">
-        <v>2400000</v>
       </c>
       <c r="P5" t="n">
         <v>2400000</v>
@@ -831,72 +839,74 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
+          <t>AC</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>EPSILON SA</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
           <t>1004000005</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>EPSILON SA</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>Telesales</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>Cameroon</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t>Aurelie Uguebou</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>15 days</t>
         </is>
       </c>
-      <c r="G6" t="n">
+      <c r="H6" t="n">
         <v>150000</v>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="I6" t="inlineStr">
         <is>
           <t>Littoral</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
+      <c r="J6" t="inlineStr">
         <is>
           <t>XAF</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>2026-05-30</t>
         </is>
       </c>
-      <c r="K6" t="n">
+      <c r="L6" t="n">
         <v>45</v>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>B</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="N6" t="inlineStr">
         <is>
           <t>Rep 1</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
+      <c r="O6" t="inlineStr">
         <is>
           <t>Douala</t>
         </is>
-      </c>
-      <c r="O6" t="n">
-        <v>75000</v>
       </c>
       <c r="P6" t="n">
         <v>75000</v>
@@ -920,16 +930,11 @@
       <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr"/>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>TOTAL</t>
-        </is>
-      </c>
-      <c r="Q7" t="n">
+      <c r="P7" t="n">
         <v>8145000</v>
       </c>
+      <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr"/>
-      <c r="S7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
